--- a/schema/excel/chemrof.xlsx
+++ b/schema/excel/chemrof.xlsx
@@ -75,26 +75,34 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AtomCation" sheetId="66" state="visible" r:id="rId66"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FullySpecifiedAtom" sheetId="67" state="visible" r:id="rId67"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="StandardInchiObject" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChemicalRole" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stereocenter" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChiralityCenter" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AtomicBond" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SubatomicParticleOccurrence" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AtomOccurrence" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChemicalSalt" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ester" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stereoisomer" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enantiomer" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RacemicMixture" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Allotrope" sheetId="80" state="visible" r:id="rId80"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PolymerRepeatUnit" sheetId="81" state="visible" r:id="rId81"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reaction" sheetId="82" state="visible" r:id="rId82"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IsomeraseReaction" sheetId="83" state="visible" r:id="rId83"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactionParticipant" sheetId="84" state="visible" r:id="rId84"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProportionalPart" sheetId="85" state="visible" r:id="rId85"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChemicalSimilarity" sheetId="86" state="visible" r:id="rId86"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoleculePairwiseSimilarity" sheetId="87" state="visible" r:id="rId87"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TanimotoSimilarity" sheetId="88" state="visible" r:id="rId88"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Concentration" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChemicalRole" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IngredientRole" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ElementSourceRole" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BufferRole" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SolventRole" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NutrientRole" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VitaminRole" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MineralNutrientRole" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stereocenter" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChiralityCenter" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AtomicBond" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SubatomicParticleOccurrence" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AtomOccurrence" sheetId="82" state="visible" r:id="rId82"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChemicalSalt" sheetId="83" state="visible" r:id="rId83"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ester" sheetId="84" state="visible" r:id="rId84"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stereoisomer" sheetId="85" state="visible" r:id="rId85"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Enantiomer" sheetId="86" state="visible" r:id="rId86"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RacemicMixture" sheetId="87" state="visible" r:id="rId87"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Allotrope" sheetId="88" state="visible" r:id="rId88"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PolymerRepeatUnit" sheetId="89" state="visible" r:id="rId89"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reaction" sheetId="90" state="visible" r:id="rId90"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IsomeraseReaction" sheetId="91" state="visible" r:id="rId91"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ReactionParticipant" sheetId="92" state="visible" r:id="rId92"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ProportionalPart" sheetId="93" state="visible" r:id="rId93"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ChemicalSimilarity" sheetId="94" state="visible" r:id="rId94"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MoleculePairwiseSimilarity" sheetId="95" state="visible" r:id="rId95"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TanimotoSimilarity" sheetId="96" state="visible" r:id="rId96"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1695,141 +1703,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2606,7 +2619,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2622,135 +2635,140 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3950,7 +3968,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3971,135 +3989,140 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8905,17 +8928,27 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>owl_subclass_of</t>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>unit</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"M,mM,uM,nM,g/L,mg/L,ug/L,ng/L,percent_w/v,percent_v/v,percent_w/w,ppm,ppb"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8974,7 +9007,15 @@
   </sheetPr>
   <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8985,9 +9026,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>source_element</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>role_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"carbon_source,nitrogen_source,phosphorus_source,sulfur_source,electron_donor,electron_acceptor,buffer,solvent,vitamin,mineral,trace_element,growth_factor,antibiotic,inducer,substrate"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8998,56 +9062,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>subject</t>
+          <t>source_element</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>object</t>
+          <t>role_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
-        <is>
-          <t>bond_type</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>bond_order</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>bond_length</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>bond_energy</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>bond_length_in_angstroms</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>bond_angle</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>torsional_angle</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
@@ -9055,8 +9084,8 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"covalent,aromatic,single,double,triple,quadruple,hydrogen,ionic,polycentric,metal-metal,salt bridge,polar covalent,sigma"</formula1>
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"carbon_source,nitrogen_source,phosphorus_source,sulfur_source,electron_donor,electron_acceptor,buffer,solvent,vitamin,mineral,trace_element,growth_factor,antibiotic,inducer,substrate"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9075,12 +9104,12 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>occurrence_of</t>
+          <t>source_element</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Count</t>
+          <t>role_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -9090,6 +9119,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"carbon_source,nitrogen_source,phosphorus_source,sulfur_source,electron_donor,electron_acceptor,buffer,solvent,vitamin,mineral,trace_element,growth_factor,antibiotic,inducer,substrate"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9100,47 +9134,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>source_element</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>occurrence_of</t>
+          <t>role_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
-        <is>
-          <t>valence</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>oxidation_number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>formal_charge</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>coordination_number</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"carbon_source,nitrogen_source,phosphorus_source,sulfur_source,electron_donor,electron_acceptor,buffer,solvent,vitamin,mineral,trace_element,growth_factor,antibiotic,inducer,substrate"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9151,147 +9170,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>inchi_atom_connections_sublayer</t>
+          <t>source_element</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>IUPAC_name</t>
+          <t>role_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
           <t>owl_subclass_of</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>type</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"carbon_source,nitrogen_source,phosphorus_source,sulfur_source,electron_donor,electron_acceptor,buffer,solvent,vitamin,mineral,trace_element,growth_factor,antibiotic,inducer,substrate"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9302,172 +9206,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>has_atom_occurrences</t>
+          <t>source_element</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>has_bonds</t>
+          <t>role_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>has_submolecules</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>has_atoms</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>is_organic</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>inchi_atom_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>IUPAC_name</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
           <t>owl_subclass_of</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>type</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"carbon_source,nitrogen_source,phosphorus_source,sulfur_source,electron_donor,electron_acceptor,buffer,solvent,vitamin,mineral,trace_element,growth_factor,antibiotic,inducer,substrate"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9478,172 +9242,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>has_atom_occurrences</t>
+          <t>source_element</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>has_bonds</t>
+          <t>role_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>has_submolecules</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>has_atoms</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>is_organic</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>inchi_atom_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>IUPAC_name</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
           <t>owl_subclass_of</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>type</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"carbon_source,nitrogen_source,phosphorus_source,sulfur_source,electron_donor,electron_acceptor,buffer,solvent,vitamin,mineral,trace_element,growth_factor,antibiotic,inducer,substrate"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9654,172 +9278,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>has_atom_occurrences</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>has_bonds</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>has_submolecules</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>has_atoms</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>is_organic</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>inchi_atom_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>IUPAC_name</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>owl_subclass_of</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -9830,162 +9291,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>has_left_enantiomer</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>has_right_enantiomer</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>chirality_agnostic_form</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>inchi_atom_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>IUPAC_name</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>owl_subclass_of</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10047,172 +9355,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>has_atom_occurrences</t>
+          <t>subject</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>has_bonds</t>
+          <t>object</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>has_submolecules</t>
+          <t>bond_type</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>has_atoms</t>
+          <t>bond_order</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>is_organic</t>
+          <t>bond_length</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>inchi_atom_connections_sublayer</t>
+          <t>bond_energy</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>IUPAC_name</t>
+          <t>bond_length_in_angstroms</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>is_radical</t>
+          <t>bond_angle</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>has_chemical_role</t>
+          <t>torsional_angle</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
           <t>owl_subclass_of</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>type</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"covalent,aromatic,single,double,triple,quadruple,hydrogen,ionic,polycentric,metal-metal,salt bridge,polar covalent,sigma"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10223,11 +9426,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
+        <is>
+          <t>occurrence_of</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
@@ -10244,93 +9457,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>left_participants</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>right_participants</t>
+          <t>occurrence_of</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>valence</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>is_diastereoselective</t>
+          <t>oxidation_number</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>is_stereo</t>
+          <t>formal_charge</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>is_balanced</t>
+          <t>coordination_number</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>is_transport</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>is_fully_characterized</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>reaction_center</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>has_rinchi_representation</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>has_reaction_smiles_representation</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>reaction_rate_coefficient</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>reaction_rate</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>reaction_type</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>type</t>
+          <t>owl_subclass_of</t>
         </is>
       </c>
     </row>
@@ -10345,91 +9508,146 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>left_participants</t>
+          <t>ph</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>right_participants</t>
+          <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>direction</t>
+          <t>IUPAC_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>is_diastereoselective</t>
+          <t>is_radical</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>is_stereo</t>
+          <t>has_chemical_role</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>is_balanced</t>
+          <t>inchi_string</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>is_transport</t>
+          <t>inchi_chemical_sublayer</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>is_fully_characterized</t>
+          <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>reaction_center</t>
+          <t>inchi_charge_sublayer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>has_rinchi_representation</t>
+          <t>inchi_proton_sublayer</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>has_reaction_smiles_representation</t>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>reaction_rate_coefficient</t>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>reaction_rate</t>
+          <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>reaction_type</t>
+          <t>inchi_isotopic_layer</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10446,13 +9664,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>has_atom_occurrences</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>has_bonds</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>has_submolecules</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>has_atoms</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>is_organic</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>type</t>
         </is>
       </c>
     </row>
@@ -10467,13 +9840,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>has_atom_occurrences</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>has_bonds</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>has_submolecules</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>has_atoms</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>is_organic</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>type</t>
         </is>
       </c>
     </row>
@@ -10488,13 +10016,168 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>has_atom_occurrences</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>has_bonds</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>has_submolecules</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>has_atoms</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>is_organic</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>type</t>
         </is>
       </c>
     </row>
@@ -10509,13 +10192,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>has_left_enantiomer</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>has_right_enantiomer</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>chirality_agnostic_form</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>type</t>
         </is>
       </c>
     </row>
@@ -10525,6 +10358,182 @@
 </file>
 
 <file path=xl/worksheets/sheet88.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AF1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>has_atom_occurrences</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>has_bonds</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>has_submolecules</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>has_atoms</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>is_organic</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet89.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -10594,4 +10603,346 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet90.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>left_participants</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>right_participants</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>is_diastereoselective</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>is_stereo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>is_balanced</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_transport</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>is_fully_characterized</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>reaction_center</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>has_rinchi_representation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>has_reaction_smiles_representation</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>reaction_rate_coefficient</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>reaction_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>reaction_type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet91.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>left_participants</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>right_participants</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>direction</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>is_diastereoselective</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>is_stereo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>is_balanced</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>is_transport</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>is_fully_characterized</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>reaction_center</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>has_rinchi_representation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>has_reaction_smiles_representation</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>reaction_rate_coefficient</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>reaction_rate</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>reaction_type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>type</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet92.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet93.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>composed_of</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>has_role</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>has_ingredient_role</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>concentration</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>minimal_percentage</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>maximum_percentage</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"active ingredient,inactive ingredient,excipient,solvent"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet94.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet95.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet96.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/schema/excel/chemrof.xlsx
+++ b/schema/excel/chemrof.xlsx
@@ -1351,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1377,140 +1377,145 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1527,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1553,140 +1558,145 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1859,7 +1869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1885,140 +1895,145 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2071,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2097,140 +2112,145 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2247,7 +2267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2273,140 +2293,145 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2423,7 +2448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2469,140 +2494,145 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2785,7 +2815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2831,140 +2861,145 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2981,7 +3016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3027,140 +3062,145 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4139,7 +4179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4165,140 +4205,145 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4315,7 +4360,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4346,140 +4391,145 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5468,7 +5518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5494,140 +5544,145 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5644,7 +5699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5670,140 +5725,145 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5820,7 +5880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5861,145 +5921,150 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6021,7 +6086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6062,145 +6127,150 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6222,7 +6292,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6263,145 +6333,150 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6423,7 +6498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6454,145 +6529,150 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6614,7 +6694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6645,145 +6725,150 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6805,7 +6890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6836,145 +6921,150 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6996,7 +7086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7032,130 +7122,135 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7177,7 +7272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7208,130 +7303,135 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7394,7 +7494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7425,130 +7525,135 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7565,7 +7670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7596,130 +7701,135 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7736,7 +7846,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7807,130 +7917,135 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7947,7 +8062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8018,130 +8133,135 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8158,7 +8278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8169,155 +8289,160 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>elemental_charge</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>atomic_number</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>has_nuclear_parts</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>owl_subclass_of</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8334,7 +8459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8345,155 +8470,160 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>elemental_charge</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>atomic_number</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>has_nuclear_parts</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>owl_subclass_of</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8510,7 +8640,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8521,155 +8651,160 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>owl_subclass_of</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>elemental_charge</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>atomic_number</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>symbol</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>has_nuclear_parts</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>owl_subclass_of</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8686,7 +8821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8722,130 +8857,135 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9664,7 +9804,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9690,140 +9830,145 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9840,166 +9985,176 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>isomeric_smiles_string</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>has_atom_occurrences</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>has_bonds</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>has_submolecules</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>has_atoms</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
         <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10016,166 +10171,196 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>enantiomer_form_of</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>absolute_configuration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>relative_configuration</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>optical_configuration</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>isomeric_smiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>has_atom_occurrences</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>has_bonds</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>has_submolecules</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>has_atoms</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
         <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10363,7 +10548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10389,140 +10574,145 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>is_organic</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>inchi_atom_connections_sublayer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>IUPAC_name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>is_radical</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>has_chemical_role</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>inchi_string</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>inchi_chemical_sublayer</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>inchi_hydrogen_connections_sublayer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>inchi_charge_sublayer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>inchi_proton_sublayer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_double_bond_sublayer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>inchi_tetrahedral_stereochemical_sublayer</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>inchi_stereochemical_type_sublayer</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>inchi_isotopic_layer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>smiles_string</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>

--- a/schema/excel/chemrof.xlsx
+++ b/schema/excel/chemrof.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,15 +550,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -575,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,15 +611,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -631,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,15 +672,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -687,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,15 +733,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -743,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,15 +784,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -789,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -815,15 +840,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -840,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,15 +901,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -896,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,15 +962,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -952,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,15 +1023,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -1008,7 +1053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1029,15 +1074,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -1090,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,15 +1166,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -1141,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,15 +1222,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -1197,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,15 +1278,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -1351,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,65 +1522,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1532,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1638,65 +1708,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1713,7 +1788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1794,65 +1869,70 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1869,7 +1949,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,65 +2055,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2086,7 +2171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2192,65 +2277,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2267,7 +2357,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2373,65 +2463,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2448,7 +2543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2574,65 +2669,70 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2649,7 +2749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2740,65 +2840,70 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2815,7 +2920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2941,65 +3046,70 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3016,7 +3126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3142,65 +3252,70 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3217,7 +3332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3293,65 +3408,70 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3368,7 +3488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3444,65 +3564,70 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3519,7 +3644,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3595,65 +3720,70 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3670,7 +3800,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3746,65 +3876,70 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3857,7 +3992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3933,65 +4068,70 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4008,7 +4148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4104,65 +4244,70 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4179,7 +4324,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4285,65 +4430,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4360,7 +4510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,65 +4621,70 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4546,7 +4701,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4622,65 +4777,70 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4697,7 +4857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4778,65 +4938,70 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4853,7 +5018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4934,65 +5099,70 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5009,7 +5179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5090,65 +5260,70 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5165,7 +5340,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5246,65 +5421,70 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5321,7 +5501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5397,65 +5577,70 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5472,7 +5657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5493,15 +5678,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -5518,7 +5708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5624,65 +5814,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5699,7 +5894,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5805,65 +6000,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5880,7 +6080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6001,70 +6201,75 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6086,7 +6291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6207,70 +6412,75 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6292,7 +6502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6413,70 +6623,75 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6498,7 +6713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6609,70 +6824,75 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6694,7 +6914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6805,70 +7025,75 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6890,7 +7115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7001,70 +7226,75 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -7086,7 +7316,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7197,60 +7427,65 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7272,7 +7507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7378,60 +7613,65 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7448,7 +7688,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7469,15 +7709,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -7494,7 +7739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7600,60 +7845,65 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7670,7 +7920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7776,60 +8026,65 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7846,7 +8101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7992,60 +8247,65 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8062,7 +8322,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AO1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8208,60 +8468,65 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8278,7 +8543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8289,160 +8554,165 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>elemental_charge</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>atomic_number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>has_nuclear_parts</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>elemental_charge</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>atomic_number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>has_nuclear_parts</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>has_part</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>IUPAC_name</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_atom_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8459,7 +8729,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8470,160 +8740,165 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>elemental_charge</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>atomic_number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>has_nuclear_parts</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>elemental_charge</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>atomic_number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>has_nuclear_parts</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>has_part</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>IUPAC_name</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_atom_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8640,7 +8915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8651,160 +8926,165 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>elemental_charge</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>atomic_number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>has_nuclear_parts</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>elemental_charge</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>atomic_number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>has_nuclear_parts</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>has_part</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>IUPAC_name</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_atom_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8821,7 +9101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8932,60 +9212,65 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9099,7 +9384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9120,15 +9405,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -9444,7 +9734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9470,15 +9760,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -9648,7 +9943,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9729,65 +10024,70 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9804,7 +10104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9910,65 +10210,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9985,7 +10290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10096,65 +10401,70 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10171,7 +10481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10302,65 +10612,70 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10377,7 +10692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10473,65 +10788,70 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10548,7 +10868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10654,65 +10974,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10750,7 +11075,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10776,15 +11101,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>extended_smiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>

--- a/schema/excel/chemrof.xlsx
+++ b/schema/excel/chemrof.xlsx
@@ -1351,7 +1351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1497,20 +1497,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1527,7 +1532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1673,20 +1678,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1703,7 +1713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1829,20 +1839,25 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1859,7 +1874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2005,20 +2020,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2071,7 +2091,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2217,20 +2237,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2247,7 +2272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2393,20 +2418,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2423,7 +2453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2589,20 +2619,25 @@
       </c>
       <c r="AG1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2619,7 +2654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AE1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2755,20 +2790,25 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2785,7 +2825,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2951,20 +2991,25 @@
       </c>
       <c r="AG1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2981,7 +3026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3147,20 +3192,25 @@
       </c>
       <c r="AG1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3177,7 +3227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3298,20 +3348,25 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3328,7 +3383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3449,20 +3504,25 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3479,7 +3539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3600,20 +3660,25 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3630,7 +3695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3751,20 +3816,25 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3817,7 +3887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3938,20 +4008,25 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3968,7 +4043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4109,20 +4184,25 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4139,7 +4219,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4285,20 +4365,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4315,7 +4400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4466,20 +4551,25 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4496,7 +4586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4617,20 +4707,25 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4647,7 +4742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4773,20 +4868,25 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4803,7 +4903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4929,20 +5029,25 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4959,7 +5064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5085,20 +5190,25 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5115,7 +5225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5241,20 +5351,25 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5271,7 +5386,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5392,20 +5507,25 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5468,7 +5588,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5614,20 +5734,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5644,7 +5769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5790,20 +5915,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5820,7 +5950,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5981,25 +6111,30 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6021,7 +6156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6182,25 +6317,30 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6222,7 +6362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AJ1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6383,25 +6523,30 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6423,7 +6568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6574,25 +6719,30 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6614,7 +6764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6765,25 +6915,30 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6805,7 +6960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6956,25 +7111,30 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6996,7 +7156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7147,15 +7307,20 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7177,7 +7342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7323,15 +7488,20 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7394,7 +7564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7540,15 +7710,20 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7565,7 +7740,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7711,15 +7886,20 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7736,7 +7916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7922,15 +8102,20 @@
       </c>
       <c r="AK1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7947,7 +8132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM1"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8133,15 +8318,20 @@
       </c>
       <c r="AK1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8158,7 +8348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8309,15 +8499,20 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8334,7 +8529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8485,15 +8680,20 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8510,7 +8710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8661,15 +8861,20 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8686,7 +8891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8837,15 +9042,20 @@
       </c>
       <c r="AD1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9508,7 +9718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9634,20 +9844,25 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9664,7 +9879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9810,20 +10025,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9840,7 +10060,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9986,20 +10206,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10016,7 +10241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10162,20 +10387,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10192,7 +10422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10333,20 +10563,25 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10363,7 +10598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10509,20 +10744,25 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>

--- a/schema/excel/chemrof.xlsx
+++ b/schema/excel/chemrof.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,15 +550,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -575,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -606,15 +611,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -631,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,15 +672,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -687,7 +702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -718,15 +733,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -743,7 +763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,15 +784,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -789,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -815,15 +840,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -840,7 +870,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,15 +901,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -896,7 +931,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,15 +962,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -952,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,15 +1023,20 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -1008,7 +1053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1029,15 +1074,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -1090,7 +1140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1116,15 +1166,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -1141,7 +1196,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1167,15 +1222,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -1197,7 +1257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1218,15 +1278,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -1351,7 +1416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,65 +1522,75 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1532,7 +1607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1638,65 +1713,75 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1713,7 +1798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1794,65 +1879,75 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -1869,7 +1964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1975,65 +2070,75 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2086,7 +2191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2192,65 +2297,75 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2267,7 +2382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2373,65 +2488,75 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2448,7 +2573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2574,65 +2699,75 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2649,7 +2784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD1"/>
+  <dimension ref="A1:AF1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2740,65 +2875,75 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -2815,7 +2960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2941,65 +3086,75 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3016,7 +3171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3142,65 +3297,75 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3217,7 +3382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3293,65 +3458,75 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3368,7 +3543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3444,65 +3619,75 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3519,7 +3704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3595,65 +3780,75 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3670,7 +3865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3746,65 +3941,75 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -3857,7 +4062,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3933,65 +4138,75 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4008,7 +4223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4104,65 +4319,75 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4179,7 +4404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4285,65 +4510,75 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4360,7 +4595,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,65 +4706,75 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4546,7 +4791,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4622,65 +4867,75 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4697,7 +4952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4778,65 +5033,75 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -4853,7 +5118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4934,65 +5199,75 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5009,7 +5284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5090,65 +5365,75 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5165,7 +5450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5246,65 +5531,75 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5321,7 +5616,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA1"/>
+  <dimension ref="A1:AC1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5397,65 +5692,75 @@
       </c>
       <c r="O1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5472,7 +5777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5493,15 +5798,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -5518,7 +5828,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5624,65 +5934,75 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5699,7 +6019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5805,65 +6125,75 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -5880,7 +6210,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6001,70 +6331,80 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6086,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6207,70 +6547,80 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6292,7 +6642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AK1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6413,70 +6763,80 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6498,7 +6858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6609,70 +6969,80 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6694,7 +7064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6805,70 +7175,80 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -6890,7 +7270,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI1"/>
+  <dimension ref="A1:AK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7001,70 +7381,80 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>elemental_charge</t>
         </is>
@@ -7086,7 +7476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7197,60 +7587,70 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7272,7 +7672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7378,60 +7778,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7448,7 +7858,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7469,15 +7879,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -7494,7 +7909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7600,60 +8015,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7670,7 +8095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7776,60 +8201,70 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -7846,7 +8281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7992,60 +8427,70 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8062,7 +8507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN1"/>
+  <dimension ref="A1:AP1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8208,60 +8653,70 @@
       </c>
       <c r="AC1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8278,7 +8733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8289,160 +8744,170 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>elemental_charge</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>atomic_number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>has_nuclear_parts</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>elemental_charge</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>atomic_number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>has_nuclear_parts</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>has_part</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>IUPAC_name</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_atom_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8459,7 +8924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8470,160 +8935,170 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>elemental_charge</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>atomic_number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>has_nuclear_parts</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>elemental_charge</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>atomic_number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>has_nuclear_parts</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>has_part</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>IUPAC_name</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_atom_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8640,7 +9115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8651,160 +9126,170 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>elemental_charge</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>atomic_number</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>has_nuclear_parts</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>has_part</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>IUPAC_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>is_radical</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>has_chemical_role</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>inchi_string</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>inchi_chemical_sublayer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>inchi_atom_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>inchi_hydrogen_connections_sublayer</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>inchi_charge_sublayer</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>inchi_proton_sublayer</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_double_bond_sublayer</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>inchi_tetrahedral_stereochemical_sublayer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>inchi_stereochemical_type_sublayer</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>inchi_isotopic_layer</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>smiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>empirical_formula</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>has_major_microspecies_at_pH7_3</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>molecular_mass</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>water_solubility</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>pka_ionization_constant</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>pka_temperature</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>pka_ionic_strength</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>pka_solvent</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>pka_pressure</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>elemental_charge</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>atomic_number</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>has_nuclear_parts</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>has_part</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>IUPAC_name</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>is_radical</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>has_chemical_role</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>inchi_string</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>inchi_chemical_sublayer</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>inchi_atom_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>inchi_hydrogen_connections_sublayer</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>inchi_charge_sublayer</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>inchi_proton_sublayer</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_double_bond_sublayer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>inchi_tetrahedral_stereochemical_sublayer</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>inchi_stereochemical_type_sublayer</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>inchi_isotopic_layer</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>smiles_string</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>empirical_formula</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>has_major_microspecies_at_pH7_3</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>molecular_mass</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>water_solubility</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>pka_ionization_constant</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>pka_temperature</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>pka_ionic_strength</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>pka_solvent</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>pka_pressure</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -8821,7 +9306,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8932,60 +9417,70 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9099,7 +9594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9120,15 +9615,20 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -9444,7 +9944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9470,15 +9970,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
@@ -9648,7 +10153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9729,65 +10234,75 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9804,7 +10319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9910,65 +10425,75 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -9985,7 +10510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH1"/>
+  <dimension ref="A1:AJ1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10096,65 +10621,75 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10171,7 +10706,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10302,65 +10837,75 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10377,7 +10922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE1"/>
+  <dimension ref="A1:AG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10473,65 +11018,75 @@
       </c>
       <c r="S1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10548,7 +11103,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AI1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10654,65 +11209,75 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
           <t>empirical_formula</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>has_major_microspecies_at_pH7_3</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>molecular_mass</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>water_solubility</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>pka_ionization_constant</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>pka_temperature</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>pka_ionic_strength</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>pka_solvent</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>pka_pressure</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>classified_by</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
         <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>type</t>
         </is>
@@ -10750,7 +11315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10776,15 +11341,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>cxsmiles_string</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>owl_subclass_of</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>subtype_of</t>
         </is>
